--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.732124598286489</v>
+        <v>1.418970247221555</v>
       </c>
       <c r="D2" t="n">
-        <v>20.74901978943156</v>
+        <v>3.371715715782629</v>
       </c>
       <c r="E2" t="n">
-        <v>28.29567384152323</v>
+        <v>4.598046999247524</v>
       </c>
       <c r="F2" t="n">
-        <v>9.277306803114111</v>
+        <v>1.507562355506043</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.32347228133294</v>
+        <v>10.6150642457166</v>
       </c>
       <c r="D3" t="n">
-        <v>39.30363339565979</v>
+        <v>6.386840426794715</v>
       </c>
       <c r="E3" t="n">
-        <v>28.29567384152323</v>
+        <v>4.598046999247524</v>
       </c>
       <c r="F3" t="n">
-        <v>9.277306803114111</v>
+        <v>1.507562355506043</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
